--- a/etf_comparison.xlsx
+++ b/etf_comparison.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Holdings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overlap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sectors" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overlap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sectors" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +28,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,8 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,628 +444,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ETF</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ETF Comparison Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NVIDIA Corp</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.07315240000000001</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SPY</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ETFS Analyzed: SPY, QQQ, VTI</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Apple Inc</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.06632059999999999</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Microsoft Corp</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.049592</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SPY</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Top Holding in ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Amazon.com Inc</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0347069</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SPY</t>
+          <t>SPY: NVIDIA Corp (7.3%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class A</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0308148</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SPY</t>
+          <t>QQQ: NVIDIA Corp (8.4%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Broadcom Inc</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.025636699</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class C</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0246022</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SPY</t>
+          <t>VTI: NVIDIA Corp (6.2%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Meta Platforms Inc Class A</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.023982301</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SPY</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Larget Sector per ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tesla Inc</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0192143</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SPY</t>
+          <t>SPY: Technology (33.08%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRK-B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Inc Class B</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.015729701</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SPY</t>
+          <t>QQQ: Technology (50.0%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NVIDIA Corp</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.08399419499999999</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Apple Inc</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0761501</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+          <t>VTI: Technology (31.11%)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Microsoft Corp</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.0569425</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Overlap Analysis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Amazon.com Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.043793503</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+          <t>VTI vs VTI: 10 stocks in common - 36.4% of SPY, 31.9% of VTI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tesla Inc</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.0391901</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+          <t>VTI vs VTI: 9 stocks in common - 43.5% of QQQ, 30.5% of VTI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Meta Platforms Inc Class A</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0371346</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class A</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0353833</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Walmart Inc</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.0336763</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class C</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.032848798</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Broadcom Inc</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0294376</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NVIDIA Corp</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0617275</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Apple Inc</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.058908</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Microsoft Corp</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.044049602</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Amazon.com Inc</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.030490201</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class A</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0273606</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Broadcom Inc</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.0227725</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Alphabet Inc Class C</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.021610899</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Meta Platforms Inc Class A</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.021303201</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tesla Inc</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.0171717</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BRK-B</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Inc Class B</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.013682701</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>VTI</t>
+          <t>VTI vs VTI: 10 stocks in common - 31.9% of VTI, 31.9% of VTI</t>
         </is>
       </c>
     </row>
@@ -1051,116 +562,634 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ETF Pair</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Stocks in Common</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Overlap Weight in SPY</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Overlap Weight in QQQ</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Shared Tickers</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Overlap Weight in VTI</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ETF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPY vs QQQ</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>34.8%</t>
-        </is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.07315240000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>SPY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPY vs VTI</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>31.9%</t>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.06632059999999999</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QQQ vs VTI</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.049592</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>30.5%</t>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0347069</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0308148</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.025636699</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0246022</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.023982301</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0192143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc Class B</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.015729701</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.08399419499999999</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0761501</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0569425</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.043793503</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0391901</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0371346</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0353833</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Walmart Inc</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0336763</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.032848798</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0294376</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0617275</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.058908</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.044049602</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.030490201</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0273606</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0227725</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.021610899</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.021303201</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0171717</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc Class B</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.013682701</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VTI</t>
         </is>
       </c>
     </row>
@@ -1175,26 +1204,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ETF Pair</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Stocks in Common</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in SPY</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in QQQ</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Shared Tickers</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SPY vs QQQ</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SPY vs VTI</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QQQ vs VTI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>VTI</t>
         </is>

--- a/etf_comparison.xlsx
+++ b/etf_comparison.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Overlap" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sectors" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Charts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,6 +154,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11430000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1546,4 +1577,18 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/etf_comparison.xlsx
+++ b/etf_comparison.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ETFS Analyzed: SPY, QQQ, VTI</t>
+          <t>ETFS Analyzed: VOO, IVV, SPY, VTI, QQQ, VTV, VUG, IEMG</t>
         </is>
       </c>
     </row>
@@ -508,77 +508,182 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPY: NVIDIA Corp (7.3%)</t>
+          <t>VOO: NVIDIA Corp (7.3%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QQQ: NVIDIA Corp (8.4%)</t>
+          <t>IVV: NVIDIA Corp (7.3%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>SPY: NVIDIA Corp (7.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>VTI: NVIDIA Corp (6.2%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Larget Sector per ETF</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QQQ: NVIDIA Corp (8.4%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPY: Technology (33.08%)</t>
+          <t>VTV: Berkshire Hathaway Inc Class B (3.1%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QQQ: Technology (50.0%)</t>
+          <t>VUG: NVIDIA Corp (12.8%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VTI: Technology (31.11%)</t>
+          <t>IEMG: Taiwan Semiconductor Manufacturing Co Ltd (11.6%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Overlap Analysis</t>
+          <t>Larget Sector per ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VTI vs VTI: 10 stocks in common - 36.4% of SPY, 31.9% of VTI</t>
+          <t>VOO: Technology (33.14%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VTI vs VTI: 9 stocks in common - 43.5% of QQQ, 30.5% of VTI</t>
+          <t>IVV: Technology (33.08%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VTI vs VTI: 10 stocks in common - 31.9% of VTI, 31.9% of VTI</t>
+          <t>SPY: Technology (33.08%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VTI: Technology (31.11%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QQQ: Technology (50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VTV: Financial Services (21.88%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VUG: Technology (50.81%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IEMG: Technology (31.91%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Overlap Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of VOO, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of IVV, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of SPY, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of VTI, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of QQQ, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of VTV, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 0 stocks in common - 0.0% of VUG, 0.0% of IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IEMG vs IEMG: 10 stocks in common - 28.9% of IEMG, 28.9% of IEMG</t>
         </is>
       </c>
     </row>
@@ -593,13 +698,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,11 +741,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07315240000000001</v>
+        <v>0.0730978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -656,11 +761,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.06632059999999999</v>
+        <v>0.066271804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -676,11 +781,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.049592</v>
+        <v>0.0495553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -696,11 +801,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0347069</v>
+        <v>0.0346825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -716,11 +821,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0308148</v>
+        <v>0.0307936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -736,11 +841,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.025636699</v>
+        <v>0.0256188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -756,11 +861,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0246022</v>
+        <v>0.024585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -776,11 +881,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.023982301</v>
+        <v>0.0239659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -796,11 +901,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0192143</v>
+        <v>0.019201301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -816,11 +921,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.015729701</v>
+        <v>0.0157195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -836,11 +941,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.08399419499999999</v>
+        <v>0.07311960000000001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
@@ -856,11 +961,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0761501</v>
+        <v>0.06629119999999999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
@@ -876,11 +981,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0569425</v>
+        <v>0.0495703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
@@ -896,131 +1001,131 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.043793503</v>
+        <v>0.0346925</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Alphabet Inc Class A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0391901</v>
+        <v>0.0308022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc Class A</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0371346</v>
+        <v>0.025626399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alphabet Inc Class A</t>
+          <t>Alphabet Inc Class C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0353833</v>
+        <v>0.0245926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Meta Platforms Inc Class A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0336763</v>
+        <v>0.0239729</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alphabet Inc Class C</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.032848798</v>
+        <v>0.0192071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Berkshire Hathaway Inc Class B</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0294376</v>
+        <v>0.0157244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IVV</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1141,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0617275</v>
+        <v>0.07315240000000001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1056,11 +1161,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.058908</v>
+        <v>0.06632059999999999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1076,11 +1181,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.044049602</v>
+        <v>0.049592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1096,11 +1201,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.030490201</v>
+        <v>0.0347069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1116,11 +1221,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0273606</v>
+        <v>0.0308148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1241,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0227725</v>
+        <v>0.025636699</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1156,11 +1261,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.021610899</v>
+        <v>0.0246022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1176,11 +1281,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.021303201</v>
+        <v>0.023982301</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1301,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0171717</v>
+        <v>0.0192143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1216,11 +1321,1011 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>0.015729701</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0617275</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.058908</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.044049602</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.030490201</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0273606</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0227725</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.021610899</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.021303201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0171717</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc Class B</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>0.013682701</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.08399419499999999</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0761501</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0569425</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.043793503</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0391901</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0371346</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0353833</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Walmart Inc</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0336763</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.032848798</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0294376</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc Class B</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0307019</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0298466</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corp</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.025015399</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.023275001</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Walmart Inc</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.0218217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Micron Technology Inc</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AbbVie Inc</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.0159534</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble Co</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.015197299</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>The Home Depot Inc</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0147385</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chevron Corp</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.0138987005</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.12816161</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.122312605</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.09148300400000001</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0568552</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0448629</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0443608</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.044116996</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.039485</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0357798</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Co</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.028217198</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2330.TW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Co Ltd</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.1161314</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Samsung Electronics Co Ltd</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0526747</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tencent Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.0312433</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SK Hynix Inc</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.029734299</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>9988.HK</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Ltd Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.0231991</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>HDFCBANK.NS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.008131299999999999</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00939</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>China Construction Bank Corp Class H</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.0072499</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2317.TW</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Hon Hai Precision Industry Co Ltd</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.0072322</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MediaTek Inc</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.0069969</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>IEMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RELIANCE.NS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.0068893</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>IEMG</t>
         </is>
       </c>
     </row>
@@ -1235,15 +2340,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="64" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1259,55 +2369,85 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Overlap Weight in VOO</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in IVV</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Shared Tickers</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Overlap Weight in SPY</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in VTI</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Overlap Weight in QQQ</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Shared Tickers</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Overlap Weight in VTI</t>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in VTV</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in VUG</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in IEMG</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPY vs QQQ</t>
+          <t>VOO vs IVV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPY vs VTI</t>
+          <t>VOO vs SPY</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1315,7 +2455,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1326,33 +2466,786 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.9%</t>
-        </is>
-      </c>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QQQ vs VTI</t>
+          <t>VOO vs VTI</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VOO vs QQQ</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>9</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VOO vs VTV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VOO vs VUG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VOO vs IEMG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IVV vs SPY</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IVV vs VTI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IVV vs QQQ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IVV vs VTV</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IVV vs VUG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IVV vs IEMG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SPY vs VTI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SPY vs QQQ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SPY vs VTV</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SPY vs VUG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SPY vs IEMG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VTI vs QQQ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>30.5%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VTI vs VTV</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VTI vs VUG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VTI vs IEMG</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QQQ vs VTV</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QQQ vs VUG</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QQQ vs IEMG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VTV vs VUG</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VTV vs IEMG</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VUG vs IEMG</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1367,13 +3260,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1384,17 +3282,42 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>VTI</t>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>VTV</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>IEMG</t>
         </is>
       </c>
     </row>
@@ -1408,10 +3331,25 @@
         <v>1.98</v>
       </c>
       <c r="C2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D2" t="n">
-        <v>2.5</v>
+      <c r="G2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -1421,13 +3359,28 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="C3" t="n">
         <v>10.11</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="F3" t="n">
         <v>12.51</v>
       </c>
-      <c r="D3" t="n">
-        <v>10.08</v>
+      <c r="G3" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.41</v>
       </c>
     </row>
     <row r="4">
@@ -1437,13 +3390,28 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C4" t="n">
         <v>1.93</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.28</v>
       </c>
-      <c r="D4" t="n">
-        <v>2.19</v>
+      <c r="G4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.76</v>
       </c>
     </row>
     <row r="5">
@@ -1453,13 +3421,28 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="C5" t="n">
         <v>5.43</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="F5" t="n">
         <v>8.59</v>
       </c>
-      <c r="D5" t="n">
-        <v>5.13</v>
+      <c r="G5" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.37</v>
       </c>
     </row>
     <row r="6">
@@ -1469,13 +3452,28 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="C6" t="n">
         <v>33.08</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="F6" t="n">
         <v>50</v>
       </c>
-      <c r="D6" t="n">
-        <v>31.11</v>
+      <c r="G6" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="I6" t="n">
+        <v>31.91</v>
       </c>
     </row>
     <row r="7">
@@ -1485,13 +3483,28 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="C7" t="n">
         <v>10.73</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F7" t="n">
         <v>16.44</v>
       </c>
-      <c r="D7" t="n">
-        <v>9.880000000000001</v>
+      <c r="G7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.99</v>
       </c>
     </row>
     <row r="8">
@@ -1501,13 +3514,28 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C8" t="n">
         <v>12.26</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.23</v>
       </c>
-      <c r="D8" t="n">
-        <v>12.37</v>
+      <c r="G8" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19.38</v>
       </c>
     </row>
     <row r="9">
@@ -1520,10 +3548,25 @@
         <v>2.49</v>
       </c>
       <c r="C9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.57</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.45</v>
+      <c r="G9" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -1533,13 +3576,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="C10" t="n">
         <v>8.66</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="F10" t="n">
         <v>3.39</v>
       </c>
-      <c r="D10" t="n">
-        <v>10.23</v>
+      <c r="G10" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.58</v>
       </c>
     </row>
     <row r="11">
@@ -1549,13 +3607,28 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.48</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.62</v>
       </c>
-      <c r="D11" t="n">
-        <v>3.64</v>
+      <c r="G11" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.57</v>
       </c>
     </row>
     <row r="12">
@@ -1565,13 +3638,28 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="C12" t="n">
         <v>9.84</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="F12" t="n">
         <v>5.26</v>
       </c>
-      <c r="D12" t="n">
-        <v>10.43</v>
+      <c r="G12" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/etf_comparison.xlsx
+++ b/etf_comparison.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ETFS Analyzed: SPY, QQQ, VTI, ARKK</t>
+          <t>ETFS Analyzed: VOO, QQQ, ARKK, VTI, SPY</t>
         </is>
       </c>
     </row>
@@ -533,98 +533,119 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPY: NVIDIA Corp (7.3%)</t>
+          <t>VOO: NVIDIA Corp (7.3%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QQQ: NVIDIA Corp (8.4%)</t>
+          <t>QQQ: NVIDIA Corp (8.7%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VTI: NVIDIA Corp (6.2%)</t>
+          <t>ARKK: Tesla Inc (10.4%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK: Tesla Inc (10.4%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+          <t>VTI: NVIDIA Corp (6.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SPY: NVIDIA Corp (7.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Larget Sector per ETF</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SPY: Technology (33.08%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QQQ: Technology (50.0%)</t>
+          <t>VOO: Technology (33.14%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VTI: Technology (31.11%)</t>
+          <t>QQQ: Technology (50.54%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKK: Healthcare (30.19%)</t>
+          <t>ARKK: Healthcare (29.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VTI: Technology (31.11%)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SPY: Technology (33.56%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Overlap Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ARKK vs ARKK: 1 stocks in common - 1.9% of SPY, 10.4% of ARKK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ARKK vs ARKK: 1 stocks in common - 3.9% of QQQ, 10.4% of ARKK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARKK vs ARKK: 1 stocks in common - 1.7% of VTI, 10.4% of ARKK</t>
+          <t>SPY vs SPY: 10 stocks in common - 36.3% of VOO, 36.4% of SPY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARKK vs ARKK: 10 stocks in common - 51.3% of ARKK, 51.3% of ARKK</t>
+          <t>SPY vs SPY: 9 stocks in common - 43.4% of QQQ, 34.8% of SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SPY vs SPY: 1 stocks in common - 10.4% of ARKK, 1.9% of SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPY vs SPY: 10 stocks in common - 31.9% of VTI, 36.4% of SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SPY vs SPY: 10 stocks in common - 36.4% of SPY, 36.4% of SPY</t>
         </is>
       </c>
     </row>
@@ -639,11 +660,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
@@ -682,11 +703,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07315240000000001</v>
+        <v>0.0730978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -702,11 +723,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.06632059999999999</v>
+        <v>0.066271804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -722,11 +743,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.049592</v>
+        <v>0.0495553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -742,11 +763,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0347069</v>
+        <v>0.0346825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -762,11 +783,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0308148</v>
+        <v>0.0307936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -782,11 +803,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.025636699</v>
+        <v>0.0256188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -802,11 +823,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0246022</v>
+        <v>0.024585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -822,11 +843,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.023982301</v>
+        <v>0.0239659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -842,11 +863,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0192143</v>
+        <v>0.019201301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -862,11 +883,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.015729701</v>
+        <v>0.0157195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>VOO</t>
         </is>
       </c>
     </row>
@@ -882,7 +903,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.08399419499999999</v>
+        <v>0.08671230000000001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -902,7 +923,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0761501</v>
+        <v>0.0762364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -922,7 +943,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0569425</v>
+        <v>0.056242198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -942,7 +963,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.043793503</v>
+        <v>0.045746103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -962,7 +983,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0391901</v>
+        <v>0.037964202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -982,7 +1003,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0371346</v>
+        <v>0.0345264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -993,16 +1014,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alphabet Inc Class A</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0353833</v>
+        <v>0.034309197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1013,16 +1034,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Alphabet Inc Class A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0336763</v>
+        <v>0.0342554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1042,7 +1063,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.032848798</v>
+        <v>0.031918097</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1062,7 +1083,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0294376</v>
+        <v>0.030026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,400 +1094,600 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NVIDIA Corp</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0617275</v>
+        <v>0.1040665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apple Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.058908</v>
+        <v>0.0621205</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Tempus AI Inc Class A common stock</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.044049602</v>
+        <v>0.048905402</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amazon.com Inc</t>
+          <t>Shopify Inc Registered Shs -A- Subord Vtg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.030490201</v>
+        <v>0.0479929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alphabet Inc Class A</t>
+          <t>Circle Internet Group Inc Ordinary Shares - Class A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0273606</v>
+        <v>0.045194604</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Coinbase Global Inc Ordinary Shares - Class A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0227725</v>
+        <v>0.044088896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alphabet Inc Class C</t>
+          <t>Robinhood Markets Inc Class A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.021610899</v>
+        <v>0.042701602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc Class A</t>
+          <t>Roku Inc Class A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.021303201</v>
+        <v>0.039868</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0171717</v>
+        <v>0.039659098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc Class B</t>
+          <t>Palantir Technologies Inc Ordinary Shares - Class A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.013682701</v>
+        <v>0.0357451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>ARKK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>NVIDIA Corp</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1043495</v>
+        <v>0.0617275</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Apple Inc</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.06925969999999999</v>
+        <v>0.058908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tempus AI Inc Class A common stock</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0522995</v>
+        <v>0.044049602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Roku Inc Class A</t>
+          <t>Amazon.com Inc</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0504594</v>
+        <v>0.030490201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shopify Inc Registered Shs -A- Subord Vtg</t>
+          <t>Alphabet Inc Class A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0441159</v>
+        <v>0.0273606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc Ordinary Shares - Class A</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0406488</v>
+        <v>0.0227725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Robinhood Markets Inc Class A</t>
+          <t>Alphabet Inc Class C</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.039859198</v>
+        <v>0.021610899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BEAM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Beam Therapeutics Inc</t>
+          <t>Meta Platforms Inc Class A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0376935</v>
+        <v>0.021303201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0374948</v>
+        <v>0.0171717</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Roblox Corp Ordinary Shares - Class A</t>
+          <t>Berkshire Hathaway Inc Class B</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0371127</v>
+        <v>0.013682701</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>VTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.07559059999999999</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Apple Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.066458</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Microsoft Corp</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.049028</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0362905</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class A</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0298607</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Broadcom Inc</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0261756</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alphabet Inc Class C</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.023929501</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc Class A</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0223206</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0186473</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Inc Class B</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.015672099</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SPY</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1489,8 +1710,9 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="64" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1506,34 +1728,39 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Overlap Weight in VOO</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in QQQ</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Shared Tickers</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in ARKK</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Overlap Weight in VTI</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Overlap Weight in SPY</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Overlap Weight in QQQ</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Shared Tickers</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Overlap Weight in VTI</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Overlap Weight in ARKK</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPY vs QQQ</t>
+          <t>VOO vs QQQ</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1546,7 +1773,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1556,87 +1783,91 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPY vs VTI</t>
+          <t>VOO vs ARKK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPY vs ARKK</t>
+          <t>VOO vs VTI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.4%</t>
-        </is>
-      </c>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QQQ vs VTI</t>
+          <t>VOO vs SPY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>43.5%</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>36.3%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>30.5%</t>
-        </is>
-      </c>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1650,7 +1881,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1658,37 +1889,151 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>10.4%</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VTI vs ARKK</t>
+          <t>QQQ vs VTI</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QQQ vs SPY</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARKK vs VTI</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>1.7%</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARKK vs SPY</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>10.4%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VTI vs SPY</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AAPL, AMZN, AVGO, BRK-B, GOOG, GOOGL, META, MSFT, NVDA, TSLA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -1703,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1711,6 +2056,7 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1721,22 +2067,27 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ARKK</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>SPY</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>ARKK</t>
         </is>
       </c>
     </row>
@@ -1753,10 +2104,13 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>2.5</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="F2" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="3">
@@ -1766,16 +2120,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.11</v>
+        <v>10.13</v>
       </c>
       <c r="C3" t="n">
-        <v>12.51</v>
+        <v>12.62</v>
       </c>
       <c r="D3" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="E3" t="n">
         <v>10.08</v>
       </c>
-      <c r="E3" t="n">
-        <v>12.93</v>
+      <c r="F3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1785,16 +2142,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="C4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>2.19</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
+      <c r="F4" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -1804,16 +2164,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.43</v>
+        <v>5.44</v>
       </c>
       <c r="C5" t="n">
-        <v>8.59</v>
+        <v>8.58</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>5.13</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
+      <c r="F5" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
@@ -1823,16 +2186,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.08</v>
+        <v>33.14</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>50.54</v>
       </c>
       <c r="D6" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="E6" t="n">
         <v>31.11</v>
       </c>
-      <c r="E6" t="n">
-        <v>24.56</v>
+      <c r="F6" t="n">
+        <v>33.56</v>
       </c>
     </row>
     <row r="7">
@@ -1842,16 +2208,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="C7" t="n">
-        <v>16.44</v>
+        <v>16.06</v>
       </c>
       <c r="D7" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E7" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="E7" t="n">
-        <v>12.06</v>
+      <c r="F7" t="n">
+        <v>10.48</v>
       </c>
     </row>
     <row r="8">
@@ -1861,16 +2230,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.26</v>
+        <v>12.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="D8" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="E8" t="n">
         <v>12.37</v>
       </c>
-      <c r="E8" t="n">
-        <v>14.15</v>
+      <c r="F8" t="n">
+        <v>12.35</v>
       </c>
     </row>
     <row r="9">
@@ -1883,13 +2255,16 @@
         <v>2.49</v>
       </c>
       <c r="C9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>2.45</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="F9" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -1899,16 +2274,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.66</v>
+        <v>8.68</v>
       </c>
       <c r="C10" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="D10" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E10" t="n">
         <v>10.23</v>
       </c>
-      <c r="E10" t="n">
-        <v>6.1</v>
+      <c r="F10" t="n">
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1918,16 +2296,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="C11" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>3.64</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
+      <c r="F11" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="12">
@@ -1937,16 +2318,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.84</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>5.26</v>
+        <v>5.11</v>
       </c>
       <c r="D12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E12" t="n">
         <v>10.43</v>
       </c>
-      <c r="E12" t="n">
-        <v>30.19</v>
+      <c r="F12" t="n">
+        <v>9.470000000000001</v>
       </c>
     </row>
   </sheetData>
